--- a/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
+++ b/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="49">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,42 +64,27 @@
     <t>淮安</t>
   </si>
   <si>
-    <t>72.4</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>146.1</t>
-  </si>
-  <si>
     <t>天津区</t>
   </si>
   <si>
     <t>天津</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>107.6</t>
-  </si>
-  <si>
     <t>苏州</t>
   </si>
   <si>
-    <t>80.7</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -115,64 +100,82 @@
     <t>银川</t>
   </si>
   <si>
-    <t>55.2</t>
-  </si>
-  <si>
     <t>河北区</t>
   </si>
   <si>
     <t>石家庄</t>
   </si>
   <si>
-    <t>91.8</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>广州</t>
   </si>
   <si>
-    <t>102.6</t>
-  </si>
-  <si>
     <t>山东区</t>
   </si>
   <si>
     <t>潍坊</t>
   </si>
   <si>
-    <t>88.4</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>115.5</t>
-  </si>
-  <si>
     <t>南通</t>
   </si>
   <si>
-    <t>95.3</t>
-  </si>
-  <si>
     <t>长沙</t>
   </si>
   <si>
-    <t>100.5</t>
-  </si>
-  <si>
     <t>浙南区</t>
   </si>
   <si>
     <t>义乌</t>
   </si>
   <si>
-    <t>196.5</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>福建区</t>
+  </si>
+  <si>
+    <t>泉州</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>佛山</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>常德</t>
+  </si>
+  <si>
+    <t>重庆区</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>江西区</t>
+  </si>
+  <si>
+    <t>横峰</t>
+  </si>
+  <si>
+    <t>陕西区</t>
+  </si>
+  <si>
+    <t>西安</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1142,8 +1145,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>72.4</v>
       </c>
       <c r="E2">
         <v>129.9</v>
@@ -1163,13 +1166,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
+      <c r="D3">
+        <v>146.1</v>
       </c>
       <c r="E3">
         <v>252.6</v>
@@ -1189,13 +1192,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>93</v>
       </c>
       <c r="E4">
         <v>130.4</v>
@@ -1215,13 +1218,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>107.6</v>
       </c>
       <c r="E5">
         <v>142.5</v>
@@ -1244,10 +1247,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>80.7</v>
       </c>
       <c r="E6">
         <v>98.2</v>
@@ -1256,10 +1259,10 @@
         <v>21.5</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1267,13 +1270,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
         <v>20</v>
+      </c>
+      <c r="D7">
+        <v>107.6</v>
       </c>
       <c r="E7">
         <v>129.4</v>
@@ -1293,13 +1296,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>55.2</v>
       </c>
       <c r="E8">
         <v>65.5</v>
@@ -1308,10 +1311,10 @@
         <v>18.5</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1319,13 +1322,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>91.8</v>
       </c>
       <c r="E9">
         <v>108.3</v>
@@ -1334,10 +1337,10 @@
         <v>17.9</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1345,13 +1348,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>102.6</v>
       </c>
       <c r="E10">
         <v>120.9</v>
@@ -1371,13 +1374,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D11">
+        <v>88.4</v>
       </c>
       <c r="E11">
         <v>103.9</v>
@@ -1386,10 +1389,10 @@
         <v>17.4</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1397,13 +1400,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>115.5</v>
       </c>
       <c r="E12">
         <v>134.6</v>
@@ -1426,10 +1429,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>95.3</v>
       </c>
       <c r="E13">
         <v>109.7</v>
@@ -1438,10 +1441,10 @@
         <v>15.1</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1449,13 +1452,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>100.5</v>
       </c>
       <c r="E14">
         <v>114.2</v>
@@ -1475,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>196.5</v>
       </c>
       <c r="E15">
         <v>195.7</v>
@@ -1494,6 +1497,1358 @@
       </c>
       <c r="H15">
         <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>72.4</v>
+      </c>
+      <c r="E16">
+        <v>133</v>
+      </c>
+      <c r="F16">
+        <v>83.6</v>
+      </c>
+      <c r="G16">
+        <v>109.7</v>
+      </c>
+      <c r="H16">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>80.7</v>
+      </c>
+      <c r="E17">
+        <v>105.7</v>
+      </c>
+      <c r="F17">
+        <v>30.9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>105.3</v>
+      </c>
+      <c r="E18">
+        <v>126.9</v>
+      </c>
+      <c r="F18">
+        <v>20.5</v>
+      </c>
+      <c r="G18">
+        <v>109.7</v>
+      </c>
+      <c r="H18">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>107.6</v>
+      </c>
+      <c r="E19">
+        <v>125.9</v>
+      </c>
+      <c r="F19">
+        <v>16.9</v>
+      </c>
+      <c r="G19">
+        <v>109.7</v>
+      </c>
+      <c r="H19">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <v>102.6</v>
+      </c>
+      <c r="E20">
+        <v>119.5</v>
+      </c>
+      <c r="F20">
+        <v>16.4</v>
+      </c>
+      <c r="G20">
+        <v>109.7</v>
+      </c>
+      <c r="H20">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21">
+        <v>88.4</v>
+      </c>
+      <c r="E21">
+        <v>102.6</v>
+      </c>
+      <c r="F21">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <v>109.4</v>
+      </c>
+      <c r="E22">
+        <v>124.3</v>
+      </c>
+      <c r="F22">
+        <v>13.5</v>
+      </c>
+      <c r="G22">
+        <v>109.7</v>
+      </c>
+      <c r="H22">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <v>55.2</v>
+      </c>
+      <c r="E23">
+        <v>62.5</v>
+      </c>
+      <c r="F23">
+        <v>13.1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24">
+        <v>146.1</v>
+      </c>
+      <c r="E24">
+        <v>164.1</v>
+      </c>
+      <c r="F24">
+        <v>12.3</v>
+      </c>
+      <c r="G24">
+        <v>109.7</v>
+      </c>
+      <c r="H24">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>115.5</v>
+      </c>
+      <c r="E25">
+        <v>124.2</v>
+      </c>
+      <c r="F25">
+        <v>7.4</v>
+      </c>
+      <c r="G25">
+        <v>109.7</v>
+      </c>
+      <c r="H25">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26">
+        <v>196.5</v>
+      </c>
+      <c r="E26">
+        <v>201.2</v>
+      </c>
+      <c r="F26">
+        <v>2.4</v>
+      </c>
+      <c r="G26">
+        <v>109.7</v>
+      </c>
+      <c r="H26">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>72.4</v>
+      </c>
+      <c r="E27">
+        <v>132.7</v>
+      </c>
+      <c r="F27">
+        <v>83.3</v>
+      </c>
+      <c r="G27">
+        <v>109.8</v>
+      </c>
+      <c r="H27">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28">
+        <v>80.7</v>
+      </c>
+      <c r="E28">
+        <v>101</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29">
+        <v>88.4</v>
+      </c>
+      <c r="E29">
+        <v>106.1</v>
+      </c>
+      <c r="F29">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>102.6</v>
+      </c>
+      <c r="E30">
+        <v>119.3</v>
+      </c>
+      <c r="F30">
+        <v>16.2</v>
+      </c>
+      <c r="G30">
+        <v>109.8</v>
+      </c>
+      <c r="H30">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31">
+        <v>109.4</v>
+      </c>
+      <c r="E31">
+        <v>126.7</v>
+      </c>
+      <c r="F31">
+        <v>15.8</v>
+      </c>
+      <c r="G31">
+        <v>109.8</v>
+      </c>
+      <c r="H31">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>107.6</v>
+      </c>
+      <c r="E32">
+        <v>124.6</v>
+      </c>
+      <c r="F32">
+        <v>15.7</v>
+      </c>
+      <c r="G32">
+        <v>109.8</v>
+      </c>
+      <c r="H32">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33">
+        <v>105.3</v>
+      </c>
+      <c r="E33">
+        <v>118.8</v>
+      </c>
+      <c r="F33">
+        <v>12.8</v>
+      </c>
+      <c r="G33">
+        <v>109.8</v>
+      </c>
+      <c r="H33">
+        <v>8.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>55.2</v>
+      </c>
+      <c r="E34">
+        <v>62.2</v>
+      </c>
+      <c r="F34">
+        <v>12.7</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35">
+        <v>95.3</v>
+      </c>
+      <c r="E35">
+        <v>105.1</v>
+      </c>
+      <c r="F35">
+        <v>10.2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>107.6</v>
+      </c>
+      <c r="E36">
+        <v>118.5</v>
+      </c>
+      <c r="F36">
+        <v>10.1</v>
+      </c>
+      <c r="G36">
+        <v>109.8</v>
+      </c>
+      <c r="H36">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37">
+        <v>103.8</v>
+      </c>
+      <c r="E37">
+        <v>114.3</v>
+      </c>
+      <c r="F37">
+        <v>10.1</v>
+      </c>
+      <c r="G37">
+        <v>109.8</v>
+      </c>
+      <c r="H37">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38">
+        <v>146.1</v>
+      </c>
+      <c r="E38">
+        <v>151.3</v>
+      </c>
+      <c r="F38">
+        <v>3.5</v>
+      </c>
+      <c r="G38">
+        <v>109.8</v>
+      </c>
+      <c r="H38">
+        <v>37.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39">
+        <v>196.5</v>
+      </c>
+      <c r="E39">
+        <v>201.1</v>
+      </c>
+      <c r="F39">
+        <v>2.3</v>
+      </c>
+      <c r="G39">
+        <v>109.8</v>
+      </c>
+      <c r="H39">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>72.4</v>
+      </c>
+      <c r="E40">
+        <v>132.7</v>
+      </c>
+      <c r="F40">
+        <v>83.3</v>
+      </c>
+      <c r="G40">
+        <v>110.5</v>
+      </c>
+      <c r="H40">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41">
+        <v>80.7</v>
+      </c>
+      <c r="E41">
+        <v>108.2</v>
+      </c>
+      <c r="F41">
+        <v>34</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42">
+        <v>88.4</v>
+      </c>
+      <c r="E42">
+        <v>105.8</v>
+      </c>
+      <c r="F42">
+        <v>19.6</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43">
+        <v>109.4</v>
+      </c>
+      <c r="E43">
+        <v>129.6</v>
+      </c>
+      <c r="F43">
+        <v>18.4</v>
+      </c>
+      <c r="G43">
+        <v>110.5</v>
+      </c>
+      <c r="H43">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44">
+        <v>102.6</v>
+      </c>
+      <c r="E44">
+        <v>119</v>
+      </c>
+      <c r="F44">
+        <v>15.9</v>
+      </c>
+      <c r="G44">
+        <v>110.5</v>
+      </c>
+      <c r="H44">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <v>55.2</v>
+      </c>
+      <c r="E45">
+        <v>64</v>
+      </c>
+      <c r="F45">
+        <v>15.9</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46">
+        <v>105.3</v>
+      </c>
+      <c r="E46">
+        <v>121.4</v>
+      </c>
+      <c r="F46">
+        <v>15.2</v>
+      </c>
+      <c r="G46">
+        <v>110.5</v>
+      </c>
+      <c r="H46">
+        <v>9.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47">
+        <v>107.6</v>
+      </c>
+      <c r="E47">
+        <v>121.1</v>
+      </c>
+      <c r="F47">
+        <v>12.5</v>
+      </c>
+      <c r="G47">
+        <v>110.5</v>
+      </c>
+      <c r="H47">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48">
+        <v>76.9</v>
+      </c>
+      <c r="E48">
+        <v>86.5</v>
+      </c>
+      <c r="F48">
+        <v>12.4</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49">
+        <v>82</v>
+      </c>
+      <c r="E49">
+        <v>91</v>
+      </c>
+      <c r="F49">
+        <v>10.9</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50">
+        <v>95.3</v>
+      </c>
+      <c r="E50">
+        <v>105.4</v>
+      </c>
+      <c r="F50">
+        <v>10.6</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51">
+        <v>103.8</v>
+      </c>
+      <c r="E51">
+        <v>114.4</v>
+      </c>
+      <c r="F51">
+        <v>10.1</v>
+      </c>
+      <c r="G51">
+        <v>110.5</v>
+      </c>
+      <c r="H51">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52">
+        <v>196.5</v>
+      </c>
+      <c r="E52">
+        <v>201.1</v>
+      </c>
+      <c r="F52">
+        <v>2.3</v>
+      </c>
+      <c r="G52">
+        <v>110.5</v>
+      </c>
+      <c r="H52">
+        <v>81.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53">
+        <v>146.1</v>
+      </c>
+      <c r="E53">
+        <v>144.2</v>
+      </c>
+      <c r="F53">
+        <v>-1.2</v>
+      </c>
+      <c r="G53">
+        <v>110.5</v>
+      </c>
+      <c r="H53">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>72.4</v>
+      </c>
+      <c r="E54">
+        <v>134.1</v>
+      </c>
+      <c r="F54">
+        <v>85.2</v>
+      </c>
+      <c r="G54">
+        <v>109.8</v>
+      </c>
+      <c r="H54">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55">
+        <v>80.7</v>
+      </c>
+      <c r="E55">
+        <v>108.5</v>
+      </c>
+      <c r="F55">
+        <v>34.3</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56">
+        <v>109.4</v>
+      </c>
+      <c r="E56">
+        <v>133.1</v>
+      </c>
+      <c r="F56">
+        <v>21.6</v>
+      </c>
+      <c r="G56">
+        <v>109.8</v>
+      </c>
+      <c r="H56">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57">
+        <v>88.4</v>
+      </c>
+      <c r="E57">
+        <v>106.6</v>
+      </c>
+      <c r="F57">
+        <v>20.6</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58">
+        <v>95.3</v>
+      </c>
+      <c r="E58">
+        <v>112.3</v>
+      </c>
+      <c r="F58">
+        <v>17.8</v>
+      </c>
+      <c r="G58">
+        <v>109.8</v>
+      </c>
+      <c r="H58">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59">
+        <v>55.2</v>
+      </c>
+      <c r="E59">
+        <v>64</v>
+      </c>
+      <c r="F59">
+        <v>15.9</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60">
+        <v>105.3</v>
+      </c>
+      <c r="E60">
+        <v>121.8</v>
+      </c>
+      <c r="F60">
+        <v>15.6</v>
+      </c>
+      <c r="G60">
+        <v>109.8</v>
+      </c>
+      <c r="H60">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61">
+        <v>107.6</v>
+      </c>
+      <c r="E61">
+        <v>122.9</v>
+      </c>
+      <c r="F61">
+        <v>14.1</v>
+      </c>
+      <c r="G61">
+        <v>109.8</v>
+      </c>
+      <c r="H61">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62">
+        <v>102.6</v>
+      </c>
+      <c r="E62">
+        <v>116.6</v>
+      </c>
+      <c r="F62">
+        <v>13.5</v>
+      </c>
+      <c r="G62">
+        <v>109.8</v>
+      </c>
+      <c r="H62">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63">
+        <v>76.9</v>
+      </c>
+      <c r="E63">
+        <v>85.7</v>
+      </c>
+      <c r="F63">
+        <v>11.4</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64">
+        <v>57.6</v>
+      </c>
+      <c r="E64">
+        <v>63.7</v>
+      </c>
+      <c r="F64">
+        <v>10.5</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65">
+        <v>119.2</v>
+      </c>
+      <c r="E65">
+        <v>122.4</v>
+      </c>
+      <c r="F65">
+        <v>2.6</v>
+      </c>
+      <c r="G65">
+        <v>109.8</v>
+      </c>
+      <c r="H65">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66">
+        <v>196.5</v>
+      </c>
+      <c r="E66">
+        <v>199.2</v>
+      </c>
+      <c r="F66">
+        <v>1.3</v>
+      </c>
+      <c r="G66">
+        <v>109.8</v>
+      </c>
+      <c r="H66">
+        <v>81.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67">
+        <v>146.1</v>
+      </c>
+      <c r="E67">
+        <v>145</v>
+      </c>
+      <c r="F67">
+        <v>-0.7</v>
+      </c>
+      <c r="G67">
+        <v>109.8</v>
+      </c>
+      <c r="H67">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
+++ b/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="61">
   <si>
     <t>岗位类型</t>
   </si>
@@ -191,6 +191,27 @@
   </si>
   <si>
     <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>济南</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
 </sst>
 </file>
@@ -806,9 +827,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1121,3110 +1145,5053 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>72.4</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>129.9</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>79.2</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>111.2</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>16.8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>146.1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>252.6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>72.8</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>111.2</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>127.1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>93</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>130.4</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>40</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>111.2</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>17.2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>107.6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>142.5</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>32.3</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>111.2</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>28.1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>80.7</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>98.2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>21.5</v>
       </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>107.6</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>129.4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>20.2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>111.2</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>16.4</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>55.2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>65.5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>18.5</v>
       </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="H8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>91.8</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>108.3</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>17.9</v>
       </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>102.6</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>120.9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>17.7</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>111.2</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>8.7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>88.4</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>103.9</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>17.4</v>
       </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="H11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>115.5</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>134.6</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>16.5</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>111.2</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>21.1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>95.3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>109.7</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>15.1</v>
       </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="H13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>100.5</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>114.2</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>13.6</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>111.2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>2.7</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>196.5</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>195.7</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-0.3</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>111.2</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>72.4</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>133</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>83.6</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>109.7</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>21.2</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="A17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>80.7</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>105.7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>30.9</v>
       </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="H17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>105.3</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>126.9</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>20.5</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>109.7</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>15.6</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>107.6</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>125.9</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>16.9</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>109.7</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>14.7</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>102.6</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>119.5</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>16.4</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>109.7</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>8.9</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>88.4</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>102.6</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>16</v>
       </c>
-      <c r="H21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="H21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="A22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>109.4</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>124.3</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>13.5</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>109.7</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>13.2</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="A23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>55.2</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>62.5</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>13.1</v>
       </c>
-      <c r="H23" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="H23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="A24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>146.1</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>164.1</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>12.3</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>109.7</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>49.5</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>115.5</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>124.2</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>7.4</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>109.7</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>13.1</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>196.5</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>201.2</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>2.4</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>109.7</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>83.3</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>72.4</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>132.7</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>83.3</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>109.8</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>20.8</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>80.7</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>101</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>25</v>
       </c>
-      <c r="H28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="H28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>88.4</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>106.1</v>
       </c>
-      <c r="G29">
-        <v>20</v>
-      </c>
-      <c r="H29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="G29" s="1">
+        <v>20</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>102.6</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>119.3</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>16.2</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>109.8</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>8.6</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>109.4</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>126.7</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>15.8</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>109.8</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>15.4</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="A32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>107.6</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>124.6</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>15.7</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>109.8</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>13.4</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="A33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>105.3</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>118.8</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>12.8</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>109.8</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="1">
         <v>8.2</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="A34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>55.2</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>62.2</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>12.7</v>
       </c>
-      <c r="H34" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="H34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="A35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>95.3</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>105.1</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="1">
         <v>10.2</v>
       </c>
-      <c r="H35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="H35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="A36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>107.6</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1">
         <v>118.5</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="1">
         <v>10.1</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>109.8</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="1">
         <v>7.9</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="A37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>103.8</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>114.3</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="1">
         <v>10.1</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>109.8</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="1">
         <v>4.1</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="A38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="1">
         <v>146.1</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>151.3</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="1">
         <v>3.5</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>109.8</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="1">
         <v>37.7</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="A39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="1">
         <v>196.5</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>201.1</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>2.3</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>109.8</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>83.1</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="1">
         <v>72.4</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1">
         <v>132.7</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="1">
         <v>83.3</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>110.5</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>20.1</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="1">
         <v>80.7</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="1">
         <v>108.2</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="1">
         <v>34</v>
       </c>
-      <c r="H41" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="H41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="1">
         <v>88.4</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="1">
         <v>105.8</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="1">
         <v>19.6</v>
       </c>
-      <c r="H42" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="H42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="1">
         <v>109.4</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="1">
         <v>129.6</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="1">
         <v>18.4</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>110.5</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="1">
         <v>17.2</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="1">
         <v>102.6</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="1">
         <v>119</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="1">
         <v>15.9</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>110.5</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="1">
         <v>7.6</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="1">
         <v>55.2</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="1">
         <v>64</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="1">
         <v>15.9</v>
       </c>
-      <c r="H45" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="H45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="1">
         <v>105.3</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="1">
         <v>121.4</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="1">
         <v>15.2</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>110.5</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="1">
         <v>9.8</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="1">
         <v>107.6</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="1">
         <v>121.1</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="1">
         <v>12.5</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>110.5</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="1">
         <v>9.5</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="1">
         <v>76.9</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1">
         <v>86.5</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="1">
         <v>12.4</v>
       </c>
-      <c r="H48" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="H48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="1">
         <v>82</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1">
         <v>91</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="1">
         <v>10.9</v>
       </c>
-      <c r="H49" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="H49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="1">
         <v>95.3</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="1">
         <v>105.4</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="1">
         <v>10.6</v>
       </c>
-      <c r="H50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="A51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="1">
         <v>103.8</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="1">
         <v>114.4</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="1">
         <v>10.1</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>110.5</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="1">
         <v>3.4</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="A52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="1">
         <v>196.5</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="1">
         <v>201.1</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="1">
         <v>2.3</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>110.5</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="1">
         <v>81.9</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="A53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="1">
         <v>146.1</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="1">
         <v>144.2</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="1">
         <v>-1.2</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
         <v>110.5</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="1">
         <v>30.5</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="A54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="1">
         <v>72.4</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="1">
         <v>134.1</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="1">
         <v>85.2</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
         <v>109.8</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="1">
         <v>22.2</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="A55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="1">
         <v>80.7</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1">
         <v>108.5</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="1">
         <v>34.3</v>
       </c>
-      <c r="H55" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="H55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="A56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="1">
         <v>109.4</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1">
         <v>133.1</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="1">
         <v>21.6</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
         <v>109.8</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="1">
         <v>21.2</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="A57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="1">
         <v>88.4</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="1">
         <v>106.6</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="1">
         <v>20.6</v>
       </c>
-      <c r="H57" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="H57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="A58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="1">
         <v>95.3</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="1">
         <v>112.3</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="1">
         <v>17.8</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
         <v>109.8</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="1">
         <v>2.3</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="A59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="1">
         <v>55.2</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="1">
         <v>64</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="1">
         <v>15.9</v>
       </c>
-      <c r="H59" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="H59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="A60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="1">
         <v>105.3</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="1">
         <v>121.8</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="1">
         <v>15.6</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>109.8</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="1">
         <v>10.9</v>
       </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="A61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="1">
         <v>107.6</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="1">
         <v>122.9</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="1">
         <v>14.1</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
         <v>109.8</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="1">
         <v>11.9</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="A62" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="1">
         <v>102.6</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="1">
         <v>116.6</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="1">
         <v>13.5</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
         <v>109.8</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="1">
         <v>6.1</v>
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="A63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="1">
         <v>76.9</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1">
         <v>85.7</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="1">
         <v>11.4</v>
       </c>
-      <c r="H63" t="s">
-        <v>20</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="H63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="A64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="1">
         <v>57.6</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1">
         <v>63.7</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="1">
         <v>10.5</v>
       </c>
-      <c r="H64" t="s">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="H64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="A65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="1">
         <v>119.2</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="1">
         <v>122.4</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="1">
         <v>2.6</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
         <v>109.8</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="1">
         <v>11.4</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="A66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="1">
         <v>196.5</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1">
         <v>199.2</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="1">
         <v>1.3</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="1">
         <v>109.8</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="1">
         <v>81.4</v>
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="A67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="1">
         <v>146.1</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1">
         <v>145</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="1">
         <v>-0.7</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
         <v>109.8</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="1">
         <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="A68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="1">
         <v>72.4</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1">
         <v>132.3</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="1">
         <v>82.6</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>109</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="1">
         <v>21.3</v>
       </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="A69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="1">
         <v>80.7</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1">
         <v>110.2</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="1">
         <v>36.5</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
         <v>109</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="1">
         <v>1.1</v>
       </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="A70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="1">
         <v>109.4</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>133.2</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="1">
         <v>21.7</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="1">
         <v>109</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="1">
         <v>22.2</v>
       </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="A71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1">
         <v>88.4</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1">
         <v>106.8</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="1">
         <v>20.8</v>
       </c>
-      <c r="H71" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="H71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="A72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="1">
         <v>105.3</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="1">
         <v>121.4</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="1">
         <v>15.2</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="1">
         <v>109</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="1">
         <v>11.4</v>
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1">
         <v>55.2</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1">
         <v>63.1</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="1">
         <v>14.3</v>
       </c>
-      <c r="H73" t="s">
-        <v>20</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="H73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="A74" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1">
         <v>95.3</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1">
         <v>107.7</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="1">
         <v>12.9</v>
       </c>
-      <c r="H74" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="H74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" t="s">
-        <v>9</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="A75" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="1">
         <v>102.6</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="1">
         <v>115.8</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="1">
         <v>12.8</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="1">
         <v>109</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="1">
         <v>6.2</v>
       </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="A76" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1">
         <v>76.9</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1">
         <v>86</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="1">
         <v>11.8</v>
       </c>
-      <c r="H76" t="s">
-        <v>20</v>
-      </c>
-      <c r="I76" t="s">
+      <c r="H76" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="A77" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="1">
         <v>119.2</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1">
         <v>122</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="1">
         <v>2.3</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="1">
         <v>109</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="1">
         <v>11.9</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="A78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1">
         <v>196.5</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1">
         <v>197.1</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="1">
         <v>0.2</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="1">
         <v>109</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="1">
         <v>80.8</v>
       </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="A79" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="1">
         <v>146.1</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="1">
         <v>144.6</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="1">
         <v>-1</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="1">
         <v>109</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="1">
         <v>32.6</v>
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="A80" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="1">
         <v>72.4</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="1">
         <v>130.8</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="1">
         <v>80.7</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="1">
         <v>107.9</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="1">
         <v>21.2</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="A81" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="1">
         <v>80.7</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="1">
         <v>111.5</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="1">
         <v>38</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="1">
         <v>107.9</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="1">
         <v>3.2</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="A82" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="1">
         <v>109.4</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="1">
         <v>131.6</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="1">
         <v>20.3</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
         <v>107.9</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="1">
         <v>21.9</v>
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="A83" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="1">
         <v>88.4</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="1">
         <v>105.2</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="1">
         <v>19</v>
       </c>
-      <c r="H83" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" t="s">
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="A84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="1">
         <v>95.3</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="1">
         <v>108.7</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="1">
         <v>14</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="1">
         <v>107.9</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="1">
         <v>0.7</v>
       </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="A85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="1">
         <v>76.9</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="1">
         <v>87.1</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="1">
         <v>13.2</v>
       </c>
-      <c r="H85" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" t="s">
+      <c r="H85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="A86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="1">
         <v>107.6</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="1">
         <v>121.8</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="1">
         <v>13.1</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="1">
         <v>107.9</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="1">
         <v>12.8</v>
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="A87" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="1">
         <v>55.2</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="1">
         <v>62.3</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="1">
         <v>12.8</v>
       </c>
-      <c r="H87" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" t="s">
+      <c r="H87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="A88" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="1">
         <v>102.6</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="1">
         <v>115.3</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="1">
         <v>12.3</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="1">
         <v>107.9</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="1">
         <v>6.8</v>
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="A89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="1">
         <v>105.3</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="1">
         <v>118.2</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="1">
         <v>12.2</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="1">
         <v>107.9</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="1">
         <v>9.5</v>
       </c>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" t="s">
-        <v>9</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="A90" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="1">
         <v>82</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="1">
         <v>90.5</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="1">
         <v>10.3</v>
       </c>
-      <c r="H90" t="s">
-        <v>20</v>
-      </c>
-      <c r="I90" t="s">
+      <c r="H90" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" t="s">
-        <v>9</v>
-      </c>
-      <c r="B91" t="s">
+      <c r="A91" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="1">
         <v>119.2</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="1">
         <v>121.1</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="1">
         <v>1.5</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="1">
         <v>107.9</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="1">
         <v>12.1</v>
       </c>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" t="s">
-        <v>9</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="A92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="1">
         <v>146.1</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="1">
         <v>145.4</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="1">
         <v>-0.4</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="1">
         <v>107.9</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="1">
         <v>34.7</v>
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B93" t="s">
+      <c r="A93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="1">
         <v>196.5</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="1">
         <v>194.2</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="1">
         <v>-1.1</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="1">
         <v>107.9</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="1">
         <v>79.9</v>
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="A94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="1">
         <v>72.4</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="1">
         <v>130</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="1">
         <v>79.5</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="1">
         <v>107.5</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="1">
         <v>20.9</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="A95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="1">
         <v>80.7</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="1">
         <v>111.7</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="1">
         <v>38.3</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="1">
         <v>107.5</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="1">
         <v>3.9</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="A96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="1">
         <v>109.4</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="1">
         <v>128.8</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="1">
         <v>17.6</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="1">
         <v>107.5</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="1">
         <v>19.8</v>
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="A97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="1">
         <v>88.4</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="1">
         <v>103.1</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="1">
         <v>16.6</v>
       </c>
-      <c r="H97" t="s">
-        <v>20</v>
-      </c>
-      <c r="I97" t="s">
+      <c r="H97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:9">
-      <c r="A98" t="s">
-        <v>9</v>
-      </c>
-      <c r="B98" t="s">
+      <c r="A98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="1">
         <v>59.1</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="1">
         <v>67.6</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="1">
         <v>14.2</v>
       </c>
-      <c r="H98" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="H98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" t="s">
-        <v>9</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="A99" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="1">
         <v>95.3</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="1">
         <v>107.1</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="1">
         <v>12.4</v>
       </c>
-      <c r="H99" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99" t="s">
+      <c r="H99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" t="s">
-        <v>9</v>
-      </c>
-      <c r="B100" t="s">
+      <c r="A100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="1">
         <v>102.6</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="1">
         <v>114.8</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="1">
         <v>11.8</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="1">
         <v>107.5</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="1">
         <v>6.8</v>
       </c>
     </row>
     <row r="101" spans="1:9">
-      <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="A101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="1">
         <v>76.9</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="1">
         <v>85.9</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="1">
         <v>11.6</v>
       </c>
-      <c r="H101" t="s">
-        <v>20</v>
-      </c>
-      <c r="I101" t="s">
+      <c r="H101" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" t="s">
-        <v>9</v>
-      </c>
-      <c r="B102" t="s">
+      <c r="A102" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="1">
         <v>105.3</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="1">
         <v>116.8</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="1">
         <v>10.9</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <v>107.5</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="1">
         <v>8.7</v>
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" t="s">
-        <v>9</v>
-      </c>
-      <c r="B103" t="s">
+      <c r="A103" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="1">
         <v>107.6</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="1">
         <v>119.4</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="1">
         <v>10.9</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>107.5</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="1">
         <v>11.1</v>
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" t="s">
-        <v>9</v>
-      </c>
-      <c r="B104" t="s">
+      <c r="A104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="1">
         <v>82</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="1">
         <v>90.6</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="1">
         <v>10.4</v>
       </c>
-      <c r="H104" t="s">
-        <v>20</v>
-      </c>
-      <c r="I104" t="s">
+      <c r="H104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" t="s">
-        <v>9</v>
-      </c>
-      <c r="B105" t="s">
+      <c r="A105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="1">
         <v>119.2</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="1">
         <v>120.7</v>
       </c>
-      <c r="G105">
+      <c r="G105" s="1">
         <v>1.2</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="1">
         <v>107.5</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="1">
         <v>12.3</v>
       </c>
     </row>
     <row r="106" spans="1:9">
-      <c r="A106" t="s">
-        <v>9</v>
-      </c>
-      <c r="B106" t="s">
+      <c r="A106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="1">
         <v>146.1</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="1">
         <v>145.9</v>
       </c>
-      <c r="G106">
+      <c r="G106" s="1">
         <v>-0.1</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="1">
         <v>107.5</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="1">
         <v>35.7</v>
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107" t="s">
+      <c r="A107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="1">
         <v>196.5</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="1">
         <v>192.8</v>
       </c>
-      <c r="G107">
+      <c r="G107" s="1">
         <v>-1.8</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="1">
         <v>107.5</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="1">
         <v>79.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F108" s="1">
+        <v>129.6</v>
+      </c>
+      <c r="G108" s="1">
+        <v>78.9</v>
+      </c>
+      <c r="H108" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I108" s="1">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F109" s="1">
+        <v>112.8</v>
+      </c>
+      <c r="G109" s="1">
+        <v>39.6</v>
+      </c>
+      <c r="H109" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I109" s="1">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110" s="1">
+        <v>109.4</v>
+      </c>
+      <c r="F110" s="1">
+        <v>130.6</v>
+      </c>
+      <c r="G110" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="H110" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I110" s="1">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F111" s="1">
+        <v>69.7</v>
+      </c>
+      <c r="G111" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" s="1">
+        <v>88.4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>102.1</v>
+      </c>
+      <c r="G112" s="1">
+        <v>15.4</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E113" s="1">
+        <v>95</v>
+      </c>
+      <c r="F113" s="1">
+        <v>106.5</v>
+      </c>
+      <c r="G113" s="1">
+        <v>12</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E114" s="1">
+        <v>82</v>
+      </c>
+      <c r="F114" s="1">
+        <v>91.6</v>
+      </c>
+      <c r="G114" s="1">
+        <v>11.7</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F115" s="1">
+        <v>114.5</v>
+      </c>
+      <c r="G115" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="H115" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I115" s="1">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="1">
+        <v>105.3</v>
+      </c>
+      <c r="F116" s="1">
+        <v>115.9</v>
+      </c>
+      <c r="G116" s="1">
+        <v>10</v>
+      </c>
+      <c r="H116" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I116" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E117" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F117" s="1">
+        <v>122.4</v>
+      </c>
+      <c r="G117" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="H117" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I117" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F118" s="1">
+        <v>147</v>
+      </c>
+      <c r="G118" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H118" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I118" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E119" s="1">
+        <v>195.7</v>
+      </c>
+      <c r="F119" s="1">
+        <v>192.1</v>
+      </c>
+      <c r="G119" s="1">
+        <v>-1.8</v>
+      </c>
+      <c r="H119" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I119" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F120" s="1">
+        <v>129.4</v>
+      </c>
+      <c r="G120" s="1">
+        <v>78.7</v>
+      </c>
+      <c r="H120" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I120" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F121" s="1">
+        <v>112.6</v>
+      </c>
+      <c r="G121" s="1">
+        <v>39.4</v>
+      </c>
+      <c r="H121" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I121" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="1">
+        <v>88.4</v>
+      </c>
+      <c r="F122" s="1">
+        <v>102.4</v>
+      </c>
+      <c r="G122" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F123" s="1">
+        <v>68.3</v>
+      </c>
+      <c r="G123" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E124" s="1">
+        <v>95</v>
+      </c>
+      <c r="F124" s="1">
+        <v>108.3</v>
+      </c>
+      <c r="G124" s="1">
+        <v>14</v>
+      </c>
+      <c r="H124" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E125" s="1">
+        <v>82</v>
+      </c>
+      <c r="F125" s="1">
+        <v>92.1</v>
+      </c>
+      <c r="G125" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E126" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F126" s="1">
+        <v>113.8</v>
+      </c>
+      <c r="G126" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="H126" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I126" s="1">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E127" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F127" s="1">
+        <v>131.9</v>
+      </c>
+      <c r="G127" s="1">
+        <v>4</v>
+      </c>
+      <c r="H127" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I127" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E128" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F128" s="1">
+        <v>121.9</v>
+      </c>
+      <c r="G128" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="H128" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I128" s="1">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F129" s="1">
+        <v>146.5</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="H129" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I129" s="1">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E130" s="1">
+        <v>196</v>
+      </c>
+      <c r="F130" s="1">
+        <v>190.7</v>
+      </c>
+      <c r="G130" s="1">
+        <v>-2.7</v>
+      </c>
+      <c r="H130" s="1">
+        <v>107.2</v>
+      </c>
+      <c r="I130" s="1">
+        <v>77.9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F131" s="1">
+        <v>129.5</v>
+      </c>
+      <c r="G131" s="1">
+        <v>78.8</v>
+      </c>
+      <c r="H131" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I131" s="1">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E132" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F132" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="G132" s="1">
+        <v>36.3</v>
+      </c>
+      <c r="H132" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I132" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133" s="1">
+        <v>88.4</v>
+      </c>
+      <c r="F133" s="1">
+        <v>102.1</v>
+      </c>
+      <c r="G133" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F134" s="1">
+        <v>68.2</v>
+      </c>
+      <c r="G134" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E135" s="1">
+        <v>95</v>
+      </c>
+      <c r="F135" s="1">
+        <v>106.7</v>
+      </c>
+      <c r="G135" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E136" s="1">
+        <v>82</v>
+      </c>
+      <c r="F136" s="1">
+        <v>91.9</v>
+      </c>
+      <c r="G136" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F137" s="1">
+        <v>113.6</v>
+      </c>
+      <c r="G137" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="H137" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I137" s="1">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F138" s="1">
+        <v>117.8</v>
+      </c>
+      <c r="G138" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="H138" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I138" s="1">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E139" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F139" s="1">
+        <v>132.8</v>
+      </c>
+      <c r="G139" s="1">
+        <v>4.6</v>
+      </c>
+      <c r="H139" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I139" s="1">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E140" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F140" s="1">
+        <v>122</v>
+      </c>
+      <c r="G140" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="H140" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I140" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F141" s="1">
+        <v>147.8</v>
+      </c>
+      <c r="G141" s="1">
+        <v>1.1</v>
+      </c>
+      <c r="H141" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I141" s="1">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E142" s="1">
+        <v>196</v>
+      </c>
+      <c r="F142" s="1">
+        <v>190.2</v>
+      </c>
+      <c r="G142" s="1">
+        <v>-2.9</v>
+      </c>
+      <c r="H142" s="1">
+        <v>106.9</v>
+      </c>
+      <c r="I142" s="1">
+        <v>77.9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F143" s="1">
+        <v>129.4</v>
+      </c>
+      <c r="G143" s="1">
+        <v>78.7</v>
+      </c>
+      <c r="H143" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I143" s="1">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F144" s="1">
+        <v>110.2</v>
+      </c>
+      <c r="G144" s="1">
+        <v>36.4</v>
+      </c>
+      <c r="H144" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I144" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" s="1">
+        <v>88.4</v>
+      </c>
+      <c r="F145" s="1">
+        <v>102.2</v>
+      </c>
+      <c r="G145" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F146" s="1">
+        <v>68.2</v>
+      </c>
+      <c r="G146" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E147" s="1">
+        <v>82</v>
+      </c>
+      <c r="F147" s="1">
+        <v>91.3</v>
+      </c>
+      <c r="G147" s="1">
+        <v>11.3</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F148" s="1">
+        <v>113.4</v>
+      </c>
+      <c r="G148" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="H148" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I148" s="1">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E149" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="F149" s="1">
+        <v>63.6</v>
+      </c>
+      <c r="G149" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" s="1">
+        <v>107.6</v>
+      </c>
+      <c r="F150" s="1">
+        <v>117.6</v>
+      </c>
+      <c r="G150" s="1">
+        <v>9.2</v>
+      </c>
+      <c r="H150" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I150" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F151" s="1">
+        <v>133.5</v>
+      </c>
+      <c r="G151" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="H151" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I151" s="1">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E152" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F152" s="1">
+        <v>121.7</v>
+      </c>
+      <c r="G152" s="1">
+        <v>2</v>
+      </c>
+      <c r="H152" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I152" s="1">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F153" s="1">
+        <v>146.9</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H153" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I153" s="1">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E154" s="1">
+        <v>196</v>
+      </c>
+      <c r="F154" s="1">
+        <v>189.9</v>
+      </c>
+      <c r="G154" s="1">
+        <v>-3.1</v>
+      </c>
+      <c r="H154" s="1">
+        <v>106.8</v>
+      </c>
+      <c r="I154" s="1">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E155" s="1">
+        <v>90.3</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1216.7</v>
+      </c>
+      <c r="G155" s="1">
+        <v>1246.2</v>
+      </c>
+      <c r="H155" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I155" s="1">
+        <v>1033.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E156" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F156" s="1">
+        <v>129.1</v>
+      </c>
+      <c r="G156" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="H156" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I156" s="1">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F157" s="1">
+        <v>109.1</v>
+      </c>
+      <c r="G157" s="1">
+        <v>35</v>
+      </c>
+      <c r="H157" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E158" s="1">
+        <v>88.4</v>
+      </c>
+      <c r="F158" s="1">
+        <v>102</v>
+      </c>
+      <c r="G158" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F159" s="1">
+        <v>67.8</v>
+      </c>
+      <c r="G159" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E160" s="1">
+        <v>82</v>
+      </c>
+      <c r="F160" s="1">
+        <v>90.9</v>
+      </c>
+      <c r="G160" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F161" s="1">
+        <v>133</v>
+      </c>
+      <c r="G161" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="H161" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I161" s="1">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E162" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F162" s="1">
+        <v>121.5</v>
+      </c>
+      <c r="G162" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="H162" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I162" s="1">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F163" s="1">
+        <v>147</v>
+      </c>
+      <c r="G163" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H163" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I163" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E164" s="1">
+        <v>196</v>
+      </c>
+      <c r="F164" s="1">
+        <v>188.8</v>
+      </c>
+      <c r="G164" s="1">
+        <v>-3.6</v>
+      </c>
+      <c r="H164" s="1">
+        <v>107.3</v>
+      </c>
+      <c r="I164" s="1">
+        <v>75.9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E165" s="1">
+        <v>90.3</v>
+      </c>
+      <c r="F165" s="1">
+        <v>1138</v>
+      </c>
+      <c r="G165" s="1">
+        <v>1159.2</v>
+      </c>
+      <c r="H165" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I165" s="1">
+        <v>955.4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" s="1">
+        <v>72.4</v>
+      </c>
+      <c r="F166" s="1">
+        <v>129.1</v>
+      </c>
+      <c r="G166" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="H166" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I166" s="1">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" s="1">
+        <v>80.7</v>
+      </c>
+      <c r="F167" s="1">
+        <v>108.6</v>
+      </c>
+      <c r="G167" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="H167" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I167" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E168" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="F168" s="1">
+        <v>65.6</v>
+      </c>
+      <c r="G168" s="1">
+        <v>13.7</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E169" s="1">
+        <v>59.1</v>
+      </c>
+      <c r="F169" s="1">
+        <v>66.9</v>
+      </c>
+      <c r="G169" s="1">
+        <v>13</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E170" s="1">
+        <v>82</v>
+      </c>
+      <c r="F170" s="1">
+        <v>90.7</v>
+      </c>
+      <c r="G170" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" s="1">
+        <v>126.8</v>
+      </c>
+      <c r="F171" s="1">
+        <v>134.8</v>
+      </c>
+      <c r="G171" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="H171" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I171" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E172" s="1">
+        <v>119.2</v>
+      </c>
+      <c r="F172" s="1">
+        <v>120.9</v>
+      </c>
+      <c r="G172" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="H172" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I172" s="1">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="1">
+        <v>146.1</v>
+      </c>
+      <c r="F173" s="1">
+        <v>146.7</v>
+      </c>
+      <c r="G173" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="H173" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I173" s="1">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E174" s="1">
+        <v>196</v>
+      </c>
+      <c r="F174" s="1">
+        <v>188.2</v>
+      </c>
+      <c r="G174" s="1">
+        <v>-3.9</v>
+      </c>
+      <c r="H174" s="1">
+        <v>107.8</v>
+      </c>
+      <c r="I174" s="1">
+        <v>74.5</v>
       </c>
     </row>
   </sheetData>

--- a/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
+++ b/source/8、绩效异常岗位/6、分拣岗/分拣岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I235"/>
+  <dimension ref="A1:I287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9429,6 +9429,1990 @@
         <v>71</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F236" t="n">
+        <v>669.2</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1060.1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>110</v>
+      </c>
+      <c r="I236" t="n">
+        <v>508.1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F237" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="G237" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="H237" t="n">
+        <v>110</v>
+      </c>
+      <c r="I237" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F238" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G238" t="n">
+        <v>24</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F239" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G239" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="G240" t="n">
+        <v>11</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>湖北区</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="F241" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="G241" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>110</v>
+      </c>
+      <c r="I241" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F242" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="G242" t="n">
+        <v>7</v>
+      </c>
+      <c r="H242" t="n">
+        <v>110</v>
+      </c>
+      <c r="I242" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F243" t="n">
+        <v>143.7</v>
+      </c>
+      <c r="G243" t="n">
+        <v>5</v>
+      </c>
+      <c r="H243" t="n">
+        <v>110</v>
+      </c>
+      <c r="I243" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F244" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="G244" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="H244" t="n">
+        <v>110</v>
+      </c>
+      <c r="I244" t="n">
+        <v>71.2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F245" t="n">
+        <v>243.2</v>
+      </c>
+      <c r="G245" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="H245" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I245" t="n">
+        <v>126.9</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F246" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="G246" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H246" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I246" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F247" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F248" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G248" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F249" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G249" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F250" t="n">
+        <v>138</v>
+      </c>
+      <c r="G250" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H250" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I250" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F251" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="G251" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H251" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I251" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="F252" t="n">
+        <v>120</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H252" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I252" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F253" t="n">
+        <v>187.9</v>
+      </c>
+      <c r="G253" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H253" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="I253" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F254" t="n">
+        <v>278.7</v>
+      </c>
+      <c r="G254" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="H254" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I254" t="n">
+        <v>159.4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F255" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="G255" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H255" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I255" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F256" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="G256" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F257" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G257" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F258" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G258" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F259" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="G259" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I259" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F260" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="G260" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H260" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I260" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="F261" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H261" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I261" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F262" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="G262" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H262" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I262" t="n">
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F263" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="G263" t="n">
+        <v>430.7</v>
+      </c>
+      <c r="H263" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I263" t="n">
+        <v>184.9</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F264" t="n">
+        <v>131</v>
+      </c>
+      <c r="G264" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="H264" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I264" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F265" t="n">
+        <v>101</v>
+      </c>
+      <c r="G265" t="n">
+        <v>25</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F266" t="n">
+        <v>66</v>
+      </c>
+      <c r="G266" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F267" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="G267" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H267" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I267" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F268" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H268" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I268" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="F269" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H269" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I269" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F270" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="G270" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="H270" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I270" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F271" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="G271" t="n">
+        <v>479.9</v>
+      </c>
+      <c r="H271" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I271" t="n">
+        <v>211.3</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F272" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="G272" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H272" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I272" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F273" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G273" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F274" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G274" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F275" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="G275" t="n">
+        <v>10</v>
+      </c>
+      <c r="H275" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F276" t="n">
+        <v>137.3</v>
+      </c>
+      <c r="G276" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H276" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I276" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F277" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="G277" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I277" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="F278" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="G278" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H278" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I278" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F279" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="G279" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H279" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="I279" t="n">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F280" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="G280" t="n">
+        <v>523.5</v>
+      </c>
+      <c r="H280" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I280" t="n">
+        <v>235.1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F281" t="n">
+        <v>131</v>
+      </c>
+      <c r="G281" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="H281" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I281" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="F282" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G282" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>江西区</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>横峰</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F283" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G283" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>福建区</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>泉州</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="F284" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="G284" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H284" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I284" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>136.9</v>
+      </c>
+      <c r="F285" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="G285" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H285" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I285" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>陕西区</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="F286" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G286" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H286" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I286" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>分拣岗</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="F287" t="n">
+        <v>186</v>
+      </c>
+      <c r="G287" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H287" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="I287" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
